--- a/data/reference/validation/ipo_master_cninfo_validation_sample.xlsx
+++ b/data/reference/validation/ipo_master_cninfo_validation_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,72 +434,102 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>company_full_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>board</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>list_date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>list_year</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>has_ipo_summary</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>股票代码_巨潮</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>招股公告日期</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>中签率公告日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>上网发行日期</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>上市日期_巨潮</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>发行价格</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>总发行数量_万股</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>募集资金净额_万元</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主承销商</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>error_msg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>stock_code_match</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>list_date_match</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>validation_issue_type</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>validation_scope_note</t>
         </is>
       </c>
     </row>
@@ -521,60 +551,86 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>江苏紫金农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2019-01-03</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2019</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>601860</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>2018-11-19</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2018-12-19</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2018-12-18</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2019-01-03</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>3.14</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>36608.8889</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>112231.5473</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>中信建投证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,62 +648,84 @@
           <t>罗博特科</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2019-01-08</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2019</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>300757</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>2018-12-24</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2018-12-27</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2018-12-26</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2019-01-08</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>21.56</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>2000</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>35197.63</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>民生证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,60 +745,86 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>上海华培数能科技(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2019</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>603121</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>2018-11-27</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2018-12-28</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2018-12-27</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>11.79</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>4500</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>47042.2038</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>国金证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -738,58 +842,80 @@
           <t>青岛银行</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>2019</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>002948</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>2018-12-05</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2019-01-07</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2019-01-04</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>4.52</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>45097.7251</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>196257.01</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,60 +935,86 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>青岛蔚蓝生物股份有限公司</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>2019</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>603739</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>2018-12-24</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2019-01-04</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2019-01-03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>10.19</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>3866.7</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>34744.0291</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>广发证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -880,62 +1032,84 @@
           <t>华林证券</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2019</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>002945</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>2018-12-10</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2019-01-09</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2019-01-08</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>3.62</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>27000</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>92082.74000000001</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>招商证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -955,60 +1129,86 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>苏州龙杰特种纤维股份有限公司</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>2019</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>603332</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>2018-12-24</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2019-01-07</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2019-01-04</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>19.44</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>2973.5</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>49982.4</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>国信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1028,48 +1228,74 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>中国外运股份有限公司</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2019-01-18</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2019</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>601598</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>2018-12-27</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2019-01-18</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>5.24</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>135163.7231</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>696779.909</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,60 +1315,86 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>青岛港国际股份有限公司</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2019-01-21</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>2019</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>601298</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>2018-12-28</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2019-01-10</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2019-01-09</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>2019-01-21</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>4.61</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>45437.6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>197892.98</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>中信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1162,60 +1414,86 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>宁波水表(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2019-01-22</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>2019</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>603700</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>2019-01-02</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2019-01-10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>2019-01-22</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>16.63</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>3909</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>59667.55</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>国元证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1235,60 +1513,86 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>明阳智慧能源集团股份公司</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>2019</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>601615</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>2019-01-02</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2019-01-14</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>4.75</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>27590</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>123538.09</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>申万宏源证券承销保荐有限责任公司</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1306,62 +1610,84 @@
           <t>新乳业</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2019-01-25</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>2019</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>002946</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>2019-01-08</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>2019-01-25</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>5.45</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>8537.1067</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>40710.71</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>中国国际金融股份有限公司</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1379,62 +1705,84 @@
           <t>康龙化成</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2019</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>300759</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>2019-01-07</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2019-01-15</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>7.66</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>6563</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>43285.35</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>东方证券承销保荐有限公司</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1452,62 +1800,84 @@
           <t>华致酒行</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2019-01-29</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2019</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>300755</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>2018-12-17</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2019-01-18</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2019-01-29</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>16.79</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>5788.8667</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>88976.46000000001</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>西部证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1527,60 +1897,86 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>南京威尔药业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>2019</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>603351</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>2019-01-14</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2019-01-17</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2019-01-16</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>35.5</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>1666.67</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>53849.7387</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>中信建投证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1598,62 +1994,84 @@
           <t>恒铭达</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>2019</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>002947</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>2019-01-14</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2019-01-24</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>18.72</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>3037.8003</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>52627.11</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>国金证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1673,60 +2091,86 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>福莱特玻璃集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2019-02-15</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>2019</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>2019-01-21</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2019-01-29</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2019-02-15</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>15000</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>25438.4951</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>广发证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1744,62 +2188,84 @@
           <t>立华股份</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2019-02-18</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>2019</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>300761</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>2019-01-22</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2019-01-31</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2019-01-30</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2019-02-18</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>29.35</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>4128</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>115000</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>中泰证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1817,62 +2283,84 @@
           <t>七彩化学</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2019-02-22</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>2019</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>300758</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>2019-01-09</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2019-02-14</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2019-02-13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>2019-02-22</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>22.09</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>2668</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>54364.39</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>长江证券承销保荐有限公司</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1892,60 +2380,86 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>上海威派格智慧水务股份有限公司</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2019-02-22</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>2019</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>603956</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2019-02-13</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2019-02-12</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>2019-02-22</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>5.7</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>4259.61</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>20419.87</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>中信建投证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1963,62 +2477,84 @@
           <t>华阳国际</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2019-02-26</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>2019</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>002949</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>2019-01-29</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>2019-02-14</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2019-02-13</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2019-02-26</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>10.51</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>4903</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>47104.47</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>中信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2038,60 +2574,86 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>西安银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>2019</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>600928</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>2019-01-15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>2019-02-20</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2019-02-19</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>4.68</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>44444.4445</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>200428.5</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>中信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2109,62 +2671,84 @@
           <t>奥美医疗</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2019-03-11</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>2019</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>002950</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>2019-02-19</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>2019-02-28</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>2019-03-11</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>11.03</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>4800</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>48069.69</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>中信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2182,58 +2766,80 @@
           <t>上海瀚讯</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2019-03-14</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>2019</v>
       </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>300762</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>2019-02-25</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>2019-03-06</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2019-03-05</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>2019-03-14</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>16.28</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>3336</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>48992.17</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2251,62 +2857,84 @@
           <t>金时科技</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2019-03-15</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>2019</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>002951</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>2019-02-26</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>2019-03-07</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2019-03-06</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>2019-03-15</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>9.94</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>4500</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>39030.89</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>中信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2324,62 +2952,84 @@
           <t>锦浪科技</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2019-03-19</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>2019</v>
       </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>300763</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>2019-03-06</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>2019-03-11</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2019-03-08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>2019-03-19</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>26.64</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>2000</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>47269.72</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>海通证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2397,62 +3047,84 @@
           <t>新诺威</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2019-03-22</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>2019</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>300765</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>2019-03-05</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2019-03-14</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>2019-03-13</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>2019-03-22</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>24.47</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>5000</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>114240.92</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>安信证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2470,62 +3142,84 @@
           <t>每日互动</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>创业板</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2019-03-25</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>2019</v>
       </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>300766</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>2019-03-04</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>2019-03-13</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2019-03-12</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>2019-03-25</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>13.08</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>4010</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>45012.54</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>东方花旗证券有限公司</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2543,62 +3237,84 @@
           <t>青农商行</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>深交所主板</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2019-03-26</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>2019</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>002958</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>2019-02-12</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2019-03-14</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2019-03-13</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>2019-03-26</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>3.96</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>55555.5556</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>215207.17</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>招商证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2618,60 +3334,86 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>上海永冠众诚新材料科技(集团)股份有限公司</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>上交所主板</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2019-03-26</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>2019</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>603681</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>2019-02-12</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>2019-03-15</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2019-03-14</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>2019-03-26</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>10</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>4164.7901</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>35995.18</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>东兴证券股份有限公司</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>巨潮 IPO 摘要接口可直接校验股票代码与上市日期，不返回公司简称和板块字段。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
